--- a/outputs/financial_report.xlsx
+++ b/outputs/financial_report.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mhxtyalo/Corporate-Intelligence-Lab/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DC07561-931A-B947-822A-FE6C504DC80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942A4E26-80E9-844E-B465-89E3A383B9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1160" windowWidth="27640" windowHeight="16840" xr2:uid="{C3F73314-4B01-834F-BEAC-B0F39B2EF12D}"/>
+    <workbookView xWindow="1060" yWindow="-15360" windowWidth="27320" windowHeight="15360" activeTab="4" xr2:uid="{C3F73314-4B01-834F-BEAC-B0F39B2EF12D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="KPIs" sheetId="2" r:id="rId2"/>
+    <sheet name="Scoring" sheetId="3" r:id="rId3"/>
+    <sheet name="Growth" sheetId="4" r:id="rId4"/>
+    <sheet name="Feuil5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -407,4 +411,40 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293138F7-5977-C744-9923-B040DC46E1EB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C97A071-7740-0149-ACF8-330D84B60A45}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC14B0D8-70A4-0942-BDFE-632E72B4B8ED}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4072CC2D-C1D9-CA4C-B7F4-739BB6C6F24E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>